--- a/AAII_Financials/Quarterly/FOXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOXX_QTR_FIN.xlsx
@@ -2149,7 +2149,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="E43" s="3">
         <v>6200</v>
@@ -2845,7 +2845,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5700</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
